--- a/Testing Data/Tagging_Accuracy_Report_1.xlsx
+++ b/Testing Data/Tagging_Accuracy_Report_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\AI Tagging\streamlit_app\Testing Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4645D65B-7C3C-4CC4-86B9-4E761673FF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AFBB9C-DCDF-4314-910D-36EE29F26D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F8AA2F7D-8C7F-4071-A008-012044EEF837}"/>
   </bookViews>
